--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/big_sister.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/big_sister.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="big_sister" sheetId="1" r:id="rId3"/>
+    <sheet name="big_sister" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -160,40 +160,6 @@
   </si>
   <si>
     <t xml:space="preserve">Ahaha, there are no angels. But it's okay, as long as #bigdaddy is here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">是谁，谁在那里？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#bigdaddy，你看，是天使？！快看…有天使！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呵呵，不好意思，我的脑袋又不对劲了。#bigdaddy…但是，如果天使真的来到这里…该有多好啊。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我们必须保护小妹妹们。没错吧，#bigdaddy…？外面的世界非常…可怕。只有这小小花园……我们的家，才是安全的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">……嗯，保护小妹妹就是我们的使命…没错吧，#bigdaddy？我们不会饶恕伤害小妹妹的人。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">可怜的小家伙…小妹妹们迷失在外面的世界。甚至不知道小小花园的存在。他们都迷路走丢了呢，#bigdaddy。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呵呵，如果天使真的存在，那该有多棒啊。天使一定会帮助我们…毕竟天使就是那样的。请去寻找小妹妹，把她们带到这里来。#bigdaddy，天使一定会帮助我们的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…呵呵，又有新的小妹妹加入到我们之中了呢，#bigdaddy。你已经不再孤身一人了，从今往后无论发生什么事我们都会保护你…对吧，#bigdaddy？
-谢谢你，天使…#bigdaddy，你认为天使存在吗？如果天使真的存在，那就太美好了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…小妹妹…我们的小妹妹…。天使真是残酷，#bigdaddy…天使对小妹妹的死冷眼旁观。我们…必须从这广阔的世界中…保护小妹妹。这里是为她们而存在的…小小…花园…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">啊哈哈，天使都是假的。但没关系，只要有#bigdaddy在就好。</t>
   </si>
 </sst>
 </file>
@@ -214,25 +180,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -265,7 +231,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -274,70 +240,70 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -351,13 +317,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -533,25 +499,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.57" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,23 +552,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -610,7 +576,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="5" t="s">
         <v>15</v>
       </c>
@@ -618,14 +584,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" ht="13.8">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="H10" s="1">
+      <c r="H10" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -634,14 +600,11 @@
       <c r="J10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="K10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" ht="13.8">
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="H11" s="1">
+      <c r="H11" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -650,14 +613,11 @@
       <c r="J11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="K11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" ht="35.05">
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="H12" s="1">
+      <c r="H12" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -666,14 +626,11 @@
       <c r="J12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" ht="46.25">
+    </row>
+    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="H13" s="1">
+      <c r="H13" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -682,14 +639,11 @@
       <c r="J13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" ht="35.05">
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="H14" s="1">
+      <c r="H14" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I14" s="6" t="s">
@@ -698,12 +652,9 @@
       <c r="J14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="K14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" ht="35.05">
-      <c r="H15" s="1">
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I15" s="6" t="s">
@@ -712,17 +663,14 @@
       <c r="J15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" ht="12.8">
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" ht="68.65">
-      <c r="H17" s="1">
+    <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I17" s="7" t="s">
@@ -731,17 +679,14 @@
       <c r="J17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" ht="13.8">
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" ht="12.8">
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D19" s="1" t="s">
         <v>32</v>
       </c>
@@ -753,7 +698,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="1" t="s">
         <v>34</v>
       </c>
@@ -761,18 +706,18 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" ht="91">
-      <c r="H26" s="1">
+    <row r="26" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -781,32 +726,29 @@
       <c r="J26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="K26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" ht="91">
+    </row>
+    <row r="27" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="1" t="n">
         <v>100</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="29" ht="12.8">
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" ht="57.45">
-      <c r="H33" s="1">
+    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I33" s="6" t="s">
@@ -815,12 +757,9 @@
       <c r="J33" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="K33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" ht="23.85">
-      <c r="H34" s="1">
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I34" s="6" t="s">
@@ -829,33 +768,30 @@
       <c r="J34" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="K34" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" ht="13.8">
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="1" t="n">
         <v>-200</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="9"/>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H21:H1048576 H4:H18 I19:I20">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/big_sister.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/big_sister.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="big_sister" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="big_sister" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="57">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -160,6 +160,40 @@
   </si>
   <si>
     <t xml:space="preserve">Ahaha, there are no angels. But it's okay, as long as #bigdaddy is here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">是谁，谁在那里？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#bigdaddy，你看，是天使？！快看…有天使！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呵呵，不好意思，我的脑袋又不对劲了。#bigdaddy…但是，如果天使真的来到这里…该有多好啊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我们必须保护小妹妹们。没错吧，#bigdaddy…？外面的世界非常…可怕。只有这小小花园……我们的家，才是安全的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">……嗯，保护小妹妹就是我们的使命…没错吧，#bigdaddy？我们不会饶恕伤害小妹妹的人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可怜的小家伙…小妹妹们迷失在外面的世界。甚至不知道小小花园的存在。他们都迷路走丢了呢，#bigdaddy。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呵呵，如果天使真的存在，那该有多棒啊。天使一定会帮助我们…毕竟天使就是那样的。请去寻找小妹妹，把她们带到这里来。#bigdaddy，天使一定会帮助我们的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…呵呵，又有新的小妹妹加入到我们之中了呢，#bigdaddy。你已经不再孤身一人了，从今往后无论发生什么事我们都会保护你…对吧，#bigdaddy？
+谢谢你，天使…#bigdaddy，你认为天使存在吗？如果天使真的存在，那就太美好了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…小妹妹…我们的小妹妹…。天使真是残酷，#bigdaddy…天使对小妹妹的死冷眼旁观。我们…必须从这广阔的世界中…保护小妹妹。这里是为她们而存在的…小小…花园…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">啊哈哈，天使都是假的。但没关系，只要有#bigdaddy在就好。</t>
   </si>
 </sst>
 </file>
@@ -180,25 +214,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -231,7 +265,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -240,70 +274,70 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -317,13 +351,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -499,25 +533,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
+    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.57" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,23 +586,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="B7" s="1" t="s">
         <v>13</v>
       </c>
@@ -576,7 +610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="D8" s="5" t="s">
         <v>15</v>
       </c>
@@ -584,14 +618,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="13.8">
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="H10" s="1" t="n">
+      <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -600,11 +634,14 @@
       <c r="J10" s="6" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" ht="13.8">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="H11" s="1" t="n">
+      <c r="H11" s="1">
         <v>2</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -613,11 +650,14 @@
       <c r="J11" s="6" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" ht="35.05">
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="H12" s="1" t="n">
+      <c r="H12" s="1">
         <v>3</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -626,11 +666,14 @@
       <c r="J12" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" ht="46.25">
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
-      <c r="H13" s="1" t="n">
+      <c r="H13" s="1">
         <v>4</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -639,11 +682,14 @@
       <c r="J13" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" ht="35.05">
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="H14" s="1" t="n">
+      <c r="H14" s="1">
         <v>5</v>
       </c>
       <c r="I14" s="6" t="s">
@@ -652,9 +698,12 @@
       <c r="J14" s="6" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H15" s="1" t="n">
+      <c r="K14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" ht="35.05">
+      <c r="H15" s="1">
         <v>6</v>
       </c>
       <c r="I15" s="6" t="s">
@@ -663,14 +712,17 @@
       <c r="J15" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="16" ht="12.8">
       <c r="A16" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H17" s="1" t="n">
+    <row r="17" ht="68.65">
+      <c r="H17" s="1">
         <v>7</v>
       </c>
       <c r="I17" s="7" t="s">
@@ -679,14 +731,17 @@
       <c r="J17" s="6" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" ht="13.8">
       <c r="A18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" ht="12.8">
       <c r="D19" s="1" t="s">
         <v>32</v>
       </c>
@@ -698,7 +753,7 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="D20" s="1" t="s">
         <v>34</v>
       </c>
@@ -706,18 +761,18 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="A25" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H26" s="1" t="n">
+    <row r="26" ht="91">
+      <c r="H26" s="1">
         <v>8</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -726,29 +781,32 @@
       <c r="J26" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" ht="91">
       <c r="D27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="1">
         <v>100</v>
       </c>
       <c r="I27" s="6"/>
       <c r="J27" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H33" s="1" t="n">
+    <row r="33" ht="57.45">
+      <c r="H33" s="1">
         <v>9</v>
       </c>
       <c r="I33" s="6" t="s">
@@ -757,9 +815,12 @@
       <c r="J33" s="9" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H34" s="1" t="n">
+      <c r="K33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" ht="23.85">
+      <c r="H34" s="1">
         <v>10</v>
       </c>
       <c r="I34" s="6" t="s">
@@ -768,30 +829,33 @@
       <c r="J34" s="9" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K34" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" ht="13.8">
       <c r="D35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E35" s="1" t="n">
+      <c r="E35" s="1">
         <v>-200</v>
       </c>
       <c r="I35" s="6"/>
       <c r="J35" s="9"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="B36" s="1" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H21:H1048576 H4:H18 I19:I20">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
